--- a/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13855C6E-DD9E-47D9-AA8B-8BB4FD3494E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57885A81-3459-4798-B4C2-28239904A3F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBA6B069-1D48-4842-AFAA-137AD730CAA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08D6A1EE-672C-44B0-BB86-22595608B11F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2887E47F-BB0B-4FD7-8CD7-10E3DAD947AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0C4E2CE-6303-4CEE-8D6A-46D9C9093904}"/>
 </file>